--- a/Intersecciones/excels/ICA-ICA-ICA.xlsx
+++ b/Intersecciones/excels/ICA-ICA-ICA.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J44"/>
+  <dimension ref="A1:J25"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -483,12 +483,12 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>l-135785</t>
+          <t>I-62755</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>110101</t>
+          <t>110102</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -503,27 +503,27 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>ICA</t>
+          <t>LA TINGUIÑA</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>-14.0668176</t>
+          <t>-14.040161</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>-75.7355</t>
+          <t>-75.706799</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>Avenida Túpac Amaru</t>
+          <t>Calle Caracas / Calle 3 de Octubre</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
@@ -535,12 +535,12 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>l-35067</t>
+          <t>I-279460</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>110101</t>
+          <t>110106</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -555,27 +555,27 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>ICA</t>
+          <t>PARCONA</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>-14.0853379</t>
+          <t>-14.0681151</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>-75.7229983</t>
+          <t>-75.6829878</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>Avenida Manuel Santana Chiri / Avenida Túpac Amaru</t>
+          <t>Avenida José Matías Manzanilla / Avenida Sinchi Roca</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
@@ -587,12 +587,12 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>l-35068</t>
+          <t>I-63663</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>110101</t>
+          <t>110102</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -607,22 +607,22 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>ICA</t>
+          <t>LA TINGUIÑA</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>-14.0853612</t>
+          <t>-14.0377339</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>-75.7230683</t>
+          <t>-75.699377</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>Avenida Túpac Amaru / Prolongación La Mar</t>
+          <t>Avenida Los Próceres / Avenida Río de Janeiro</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
@@ -639,12 +639,12 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>l-35085</t>
+          <t>I-365342</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>110101</t>
+          <t>110112</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -659,22 +659,22 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>ICA</t>
+          <t>SUBTANJALLA</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>-14.0799835</t>
+          <t>-14.0293972</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>-75.722062</t>
+          <t>-75.7543906</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>Avenida Luis Jerónimo de Cabrera / Avenida Manuel Santana Chiri / Calle Abraham Valdelomar</t>
+          <t>Primavera / Calle s / n</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
@@ -691,7 +691,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>l-35111</t>
+          <t>I-555561</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -716,17 +716,17 @@
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>-14.0799549</t>
+          <t>-14.0647557</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>-75.7219198</t>
+          <t>-75.7336359</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>Avenida Luis Jerónimo de Cabrera / Avenida Manuel Santana Chiri / Calle Abraham Valdelomar / Prolongación Abraham Valdelomar</t>
+          <t>José Matías Manzanilla / Calle s / n</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
@@ -743,7 +743,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>l-35115</t>
+          <t>I-620729</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -768,22 +768,22 @@
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>-14.0711765</t>
+          <t>-14.0659359</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>-75.7354231</t>
+          <t>-75.7376298</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>Avenida Ayabaca / Avenida Túpac Amaru</t>
+          <t>José Matías Manzanilla / Calle s / n</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
@@ -795,7 +795,7 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>l-35120</t>
+          <t>I-62646</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -820,17 +820,17 @@
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>-14.07795</t>
+          <t>-14.0598238</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>-75.732735</t>
+          <t>-75.7370205</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>Avenida Túpac Amaru</t>
+          <t>Avenida Abraham Valdelomar / Avenida Arenales</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
@@ -847,7 +847,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>l-35407</t>
+          <t>I-64909</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -872,17 +872,17 @@
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>-14.0710871</t>
+          <t>-14.0663187</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>-75.7354248</t>
+          <t>-75.7355003</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>Avenida Ayabaca / Avenida Túpac Amaru</t>
+          <t>Avenida Túpac Amaru / Calle Luis Medina</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
@@ -899,12 +899,12 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>l-35408</t>
+          <t>I-281286</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>110101</t>
+          <t>110110</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -919,22 +919,22 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>ICA</t>
+          <t>SAN JUAN BAUTISTA</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>-14.0710809</t>
+          <t>-14.0047952</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>-75.7353285</t>
+          <t>-75.7530311</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>Avenida Ayabaca / Avenida Túpac Amaru</t>
+          <t>Calle s / n / Calle s / n</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
@@ -951,12 +951,12 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>l-35483</t>
+          <t>I-492495</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>110101</t>
+          <t>110112</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -971,27 +971,27 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>ICA</t>
+          <t>SUBTANJALLA</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>-14.0645889</t>
+          <t>-14.018372</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>-75.7368805</t>
+          <t>-75.7652824</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>Fermín Tangüis / Sebastian Barranca</t>
+          <t>Calle s / n / Calle s / n</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
@@ -1003,12 +1003,12 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>l-386979</t>
+          <t>I-62399</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>110101</t>
+          <t>110110</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -1023,27 +1023,27 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>ICA</t>
+          <t>SAN JUAN BAUTISTA</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>-14.0855529</t>
+          <t>-14.0300868</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>-75.7230874</t>
+          <t>-75.7379605</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>Avenida Manuel Santana Chiri / Avenida Túpac Amaru</t>
+          <t>Calle s / n / Calle s / n</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
@@ -1055,12 +1055,12 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>l-387003</t>
+          <t>I-490631</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>110101</t>
+          <t>110110</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
@@ -1075,27 +1075,27 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>ICA</t>
+          <t>SAN JUAN BAUTISTA</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>-14.0855341</t>
+          <t>-14.0269422</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>-75.7231348</t>
+          <t>-75.7352301</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>Avenida Túpac Amaru / Prolongación La Mar</t>
+          <t>Avenida Jorge Chávez / Calle s / n</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
@@ -1107,12 +1107,12 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>l-394659</t>
+          <t>I-490629</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>110101</t>
+          <t>110110</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
@@ -1127,27 +1127,27 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>ICA</t>
+          <t>SAN JUAN BAUTISTA</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>-14.0905668</t>
+          <t>-14.0258685</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>-75.7439109</t>
+          <t>-75.7346654</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Avenida Jorge Chávez / Calle s / n</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="J14" t="inlineStr">
@@ -1159,7 +1159,7 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>l-394660</t>
+          <t>I-394660</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1194,7 +1194,7 @@
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Calle s / n / Calle s / n</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
@@ -1211,7 +1211,7 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>l-394662</t>
+          <t>I-488935</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1236,17 +1236,17 @@
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>-14.0907812</t>
+          <t>-14.0740559</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>-75.7438159</t>
+          <t>-75.7848412</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Calle s / n / Calle s / n</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
@@ -1263,7 +1263,7 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>l-434036</t>
+          <t>I-62502</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1288,17 +1288,17 @@
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>-14.0778663</t>
+          <t>-14.0806734</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>-75.7325411</t>
+          <t>-75.7322198</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>Avenida Túpac Amaru</t>
+          <t>Calle s / n / Calle s / n</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
@@ -1315,12 +1315,12 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>l-434038</t>
+          <t>I-205359</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>110101</t>
+          <t>110111</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
@@ -1335,27 +1335,27 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>ICA</t>
+          <t>SANTIAGO</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>-14.0711649</t>
+          <t>-14.1746258</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>-75.7353268</t>
+          <t>-75.6858999</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>Avenida Ayabaca / Avenida Túpac Amaru</t>
+          <t>Calle s / n / Calle s / n</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="J18" t="inlineStr">
@@ -1367,7 +1367,7 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>l-434040</t>
+          <t>I-64495</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1392,17 +1392,17 @@
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>-14.0779532</t>
+          <t>-14.0689648</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>-75.7327361</t>
+          <t>-75.7354703</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>Avenida Portales</t>
+          <t>Avenida Túpac Amaru / Calle s / n</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
@@ -1419,12 +1419,12 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>l-488935</t>
+          <t>I-62243</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>110101</t>
+          <t>110112</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
@@ -1439,27 +1439,27 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>ICA</t>
+          <t>SUBTANJALLA</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>-14.0740559</t>
+          <t>-14.0199894</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>-75.7848412</t>
+          <t>-75.7544522</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Avenida San Martín / Calle General Salas</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="J20" t="inlineStr">
@@ -1471,12 +1471,12 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>l-555561</t>
+          <t>I-399404</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>110101</t>
+          <t>110110</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
@@ -1491,27 +1491,27 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>ICA</t>
+          <t>SAN JUAN BAUTISTA</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>-14.0647557</t>
+          <t>-14.0319673</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>-75.7336359</t>
+          <t>-75.7349809</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>José Matías Manzanilla</t>
+          <t>Avenida Jorge Chávez / Calle s / n</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="J21" t="inlineStr">
@@ -1523,12 +1523,12 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>l-555565</t>
+          <t>I-490628</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>110101</t>
+          <t>110110</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
@@ -1543,27 +1543,27 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>ICA</t>
+          <t>SAN JUAN BAUTISTA</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>-14.0647266</t>
+          <t>-14.0282295</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>-75.7335314</t>
+          <t>-75.7357678</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>Fray Ramon Rojas / José Matías Manzanilla</t>
+          <t>Avenida Jorge Chávez / Calle s / n</t>
         </is>
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="J22" t="inlineStr">
@@ -1575,12 +1575,12 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>l-594469</t>
+          <t>I-399413</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>110101</t>
+          <t>110110</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
@@ -1595,27 +1595,27 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>ICA</t>
+          <t>SAN JUAN BAUTISTA</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>-14.0646456</t>
+          <t>-14.0332703</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>-75.7335552</t>
+          <t>-75.7347087</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>Fray Ramon Rojas</t>
+          <t>Avenida Jorge Chávez / Calle s / n</t>
         </is>
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="J23" t="inlineStr">
@@ -1627,12 +1627,12 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>l-620727</t>
+          <t>I-399407</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>110101</t>
+          <t>110110</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
@@ -1647,27 +1647,27 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>ICA</t>
+          <t>SAN JUAN BAUTISTA</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>-14.0660386</t>
+          <t>-14.0361951</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>-75.7380044</t>
+          <t>-75.7340117</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>José Matías Manzanilla</t>
+          <t>Andrés Avelino Cáceres / Avenida Jorge Chávez</t>
         </is>
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="J24" t="inlineStr">
@@ -1679,12 +1679,12 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>l-620728</t>
+          <t>I-399405</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>110101</t>
+          <t>110110</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
@@ -1699,1018 +1699,30 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>ICA</t>
+          <t>SAN JUAN BAUTISTA</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>-14.0647682</t>
+          <t>-14.0292004</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>-75.7335198</t>
+          <t>-75.735677</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>Fray Ramon Rojas / José Matías Manzanilla</t>
+          <t>Avenida Jorge Chávez / Calle 7</t>
         </is>
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="J25" t="inlineStr">
-        <is>
-          <t>110101</t>
-        </is>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26" t="inlineStr">
-        <is>
-          <t>l-620729</t>
-        </is>
-      </c>
-      <c r="B26" t="inlineStr">
-        <is>
-          <t>110101</t>
-        </is>
-      </c>
-      <c r="C26" t="inlineStr">
-        <is>
-          <t>ICA</t>
-        </is>
-      </c>
-      <c r="D26" t="inlineStr">
-        <is>
-          <t>ICA</t>
-        </is>
-      </c>
-      <c r="E26" t="inlineStr">
-        <is>
-          <t>ICA</t>
-        </is>
-      </c>
-      <c r="F26" t="inlineStr">
-        <is>
-          <t>-14.0659359</t>
-        </is>
-      </c>
-      <c r="G26" t="inlineStr">
-        <is>
-          <t>-75.7376298</t>
-        </is>
-      </c>
-      <c r="H26" t="inlineStr">
-        <is>
-          <t>José Matías Manzanilla</t>
-        </is>
-      </c>
-      <c r="I26" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J26" t="inlineStr">
-        <is>
-          <t>110101</t>
-        </is>
-      </c>
-    </row>
-    <row r="27">
-      <c r="A27" t="inlineStr">
-        <is>
-          <t>l-62502</t>
-        </is>
-      </c>
-      <c r="B27" t="inlineStr">
-        <is>
-          <t>110101</t>
-        </is>
-      </c>
-      <c r="C27" t="inlineStr">
-        <is>
-          <t>ICA</t>
-        </is>
-      </c>
-      <c r="D27" t="inlineStr">
-        <is>
-          <t>ICA</t>
-        </is>
-      </c>
-      <c r="E27" t="inlineStr">
-        <is>
-          <t>ICA</t>
-        </is>
-      </c>
-      <c r="F27" t="inlineStr">
-        <is>
-          <t>-14.0806734</t>
-        </is>
-      </c>
-      <c r="G27" t="inlineStr">
-        <is>
-          <t>-75.7322198</t>
-        </is>
-      </c>
-      <c r="H27" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="I27" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J27" t="inlineStr">
-        <is>
-          <t>110101</t>
-        </is>
-      </c>
-    </row>
-    <row r="28">
-      <c r="A28" t="inlineStr">
-        <is>
-          <t>l-62505</t>
-        </is>
-      </c>
-      <c r="B28" t="inlineStr">
-        <is>
-          <t>110101</t>
-        </is>
-      </c>
-      <c r="C28" t="inlineStr">
-        <is>
-          <t>ICA</t>
-        </is>
-      </c>
-      <c r="D28" t="inlineStr">
-        <is>
-          <t>ICA</t>
-        </is>
-      </c>
-      <c r="E28" t="inlineStr">
-        <is>
-          <t>ICA</t>
-        </is>
-      </c>
-      <c r="F28" t="inlineStr">
-        <is>
-          <t>-14.0813042</t>
-        </is>
-      </c>
-      <c r="G28" t="inlineStr">
-        <is>
-          <t>-75.7317247</t>
-        </is>
-      </c>
-      <c r="H28" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="I28" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J28" t="inlineStr">
-        <is>
-          <t>110101</t>
-        </is>
-      </c>
-    </row>
-    <row r="29">
-      <c r="A29" t="inlineStr">
-        <is>
-          <t>l-62646</t>
-        </is>
-      </c>
-      <c r="B29" t="inlineStr">
-        <is>
-          <t>110101</t>
-        </is>
-      </c>
-      <c r="C29" t="inlineStr">
-        <is>
-          <t>ICA</t>
-        </is>
-      </c>
-      <c r="D29" t="inlineStr">
-        <is>
-          <t>ICA</t>
-        </is>
-      </c>
-      <c r="E29" t="inlineStr">
-        <is>
-          <t>ICA</t>
-        </is>
-      </c>
-      <c r="F29" t="inlineStr">
-        <is>
-          <t>-14.0598238</t>
-        </is>
-      </c>
-      <c r="G29" t="inlineStr">
-        <is>
-          <t>-75.7370205</t>
-        </is>
-      </c>
-      <c r="H29" t="inlineStr">
-        <is>
-          <t>Avenida Abraham Valdelomar / Avenida Arenales</t>
-        </is>
-      </c>
-      <c r="I29" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J29" t="inlineStr">
-        <is>
-          <t>110101</t>
-        </is>
-      </c>
-    </row>
-    <row r="30">
-      <c r="A30" t="inlineStr">
-        <is>
-          <t>l-63556</t>
-        </is>
-      </c>
-      <c r="B30" t="inlineStr">
-        <is>
-          <t>110101</t>
-        </is>
-      </c>
-      <c r="C30" t="inlineStr">
-        <is>
-          <t>ICA</t>
-        </is>
-      </c>
-      <c r="D30" t="inlineStr">
-        <is>
-          <t>ICA</t>
-        </is>
-      </c>
-      <c r="E30" t="inlineStr">
-        <is>
-          <t>ICA</t>
-        </is>
-      </c>
-      <c r="F30" t="inlineStr">
-        <is>
-          <t>-14.0597341</t>
-        </is>
-      </c>
-      <c r="G30" t="inlineStr">
-        <is>
-          <t>-75.7369204</t>
-        </is>
-      </c>
-      <c r="H30" t="inlineStr">
-        <is>
-          <t>Avenida Abraham Valdelomar / Avenida Arenales</t>
-        </is>
-      </c>
-      <c r="I30" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J30" t="inlineStr">
-        <is>
-          <t>110101</t>
-        </is>
-      </c>
-    </row>
-    <row r="31">
-      <c r="A31" t="inlineStr">
-        <is>
-          <t>l-63557</t>
-        </is>
-      </c>
-      <c r="B31" t="inlineStr">
-        <is>
-          <t>110101</t>
-        </is>
-      </c>
-      <c r="C31" t="inlineStr">
-        <is>
-          <t>ICA</t>
-        </is>
-      </c>
-      <c r="D31" t="inlineStr">
-        <is>
-          <t>ICA</t>
-        </is>
-      </c>
-      <c r="E31" t="inlineStr">
-        <is>
-          <t>ICA</t>
-        </is>
-      </c>
-      <c r="F31" t="inlineStr">
-        <is>
-          <t>-14.0594129</t>
-        </is>
-      </c>
-      <c r="G31" t="inlineStr">
-        <is>
-          <t>-75.7374781</t>
-        </is>
-      </c>
-      <c r="H31" t="inlineStr">
-        <is>
-          <t>Avenida Arenales</t>
-        </is>
-      </c>
-      <c r="I31" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J31" t="inlineStr">
-        <is>
-          <t>110101</t>
-        </is>
-      </c>
-    </row>
-    <row r="32">
-      <c r="A32" t="inlineStr">
-        <is>
-          <t>l-64282</t>
-        </is>
-      </c>
-      <c r="B32" t="inlineStr">
-        <is>
-          <t>110101</t>
-        </is>
-      </c>
-      <c r="C32" t="inlineStr">
-        <is>
-          <t>ICA</t>
-        </is>
-      </c>
-      <c r="D32" t="inlineStr">
-        <is>
-          <t>ICA</t>
-        </is>
-      </c>
-      <c r="E32" t="inlineStr">
-        <is>
-          <t>ICA</t>
-        </is>
-      </c>
-      <c r="F32" t="inlineStr">
-        <is>
-          <t>-14.0660965</t>
-        </is>
-      </c>
-      <c r="G32" t="inlineStr">
-        <is>
-          <t>-75.7384971</t>
-        </is>
-      </c>
-      <c r="H32" t="inlineStr">
-        <is>
-          <t>Calle Benedicta de Luces / José Matías Manzanilla</t>
-        </is>
-      </c>
-      <c r="I32" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="J32" t="inlineStr">
-        <is>
-          <t>110101</t>
-        </is>
-      </c>
-    </row>
-    <row r="33">
-      <c r="A33" t="inlineStr">
-        <is>
-          <t>l-64283</t>
-        </is>
-      </c>
-      <c r="B33" t="inlineStr">
-        <is>
-          <t>110101</t>
-        </is>
-      </c>
-      <c r="C33" t="inlineStr">
-        <is>
-          <t>ICA</t>
-        </is>
-      </c>
-      <c r="D33" t="inlineStr">
-        <is>
-          <t>ICA</t>
-        </is>
-      </c>
-      <c r="E33" t="inlineStr">
-        <is>
-          <t>ICA</t>
-        </is>
-      </c>
-      <c r="F33" t="inlineStr">
-        <is>
-          <t>-14.0661674</t>
-        </is>
-      </c>
-      <c r="G33" t="inlineStr">
-        <is>
-          <t>-75.7384742</t>
-        </is>
-      </c>
-      <c r="H33" t="inlineStr">
-        <is>
-          <t>Calle Benedicta de Luces / José Matías Manzanilla</t>
-        </is>
-      </c>
-      <c r="I33" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="J33" t="inlineStr">
-        <is>
-          <t>110101</t>
-        </is>
-      </c>
-    </row>
-    <row r="34">
-      <c r="A34" t="inlineStr">
-        <is>
-          <t>l-64495</t>
-        </is>
-      </c>
-      <c r="B34" t="inlineStr">
-        <is>
-          <t>110101</t>
-        </is>
-      </c>
-      <c r="C34" t="inlineStr">
-        <is>
-          <t>ICA</t>
-        </is>
-      </c>
-      <c r="D34" t="inlineStr">
-        <is>
-          <t>ICA</t>
-        </is>
-      </c>
-      <c r="E34" t="inlineStr">
-        <is>
-          <t>ICA</t>
-        </is>
-      </c>
-      <c r="F34" t="inlineStr">
-        <is>
-          <t>-14.0689648</t>
-        </is>
-      </c>
-      <c r="G34" t="inlineStr">
-        <is>
-          <t>-75.7354703</t>
-        </is>
-      </c>
-      <c r="H34" t="inlineStr">
-        <is>
-          <t>Avenida Túpac Amaru</t>
-        </is>
-      </c>
-      <c r="I34" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J34" t="inlineStr">
-        <is>
-          <t>110101</t>
-        </is>
-      </c>
-    </row>
-    <row r="35">
-      <c r="A35" t="inlineStr">
-        <is>
-          <t>l-64566</t>
-        </is>
-      </c>
-      <c r="B35" t="inlineStr">
-        <is>
-          <t>110101</t>
-        </is>
-      </c>
-      <c r="C35" t="inlineStr">
-        <is>
-          <t>ICA</t>
-        </is>
-      </c>
-      <c r="D35" t="inlineStr">
-        <is>
-          <t>ICA</t>
-        </is>
-      </c>
-      <c r="E35" t="inlineStr">
-        <is>
-          <t>ICA</t>
-        </is>
-      </c>
-      <c r="F35" t="inlineStr">
-        <is>
-          <t>-14.056181</t>
-        </is>
-      </c>
-      <c r="G35" t="inlineStr">
-        <is>
-          <t>-75.7285582</t>
-        </is>
-      </c>
-      <c r="H35" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="I35" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J35" t="inlineStr">
-        <is>
-          <t>110101</t>
-        </is>
-      </c>
-    </row>
-    <row r="36">
-      <c r="A36" t="inlineStr">
-        <is>
-          <t>l-64638</t>
-        </is>
-      </c>
-      <c r="B36" t="inlineStr">
-        <is>
-          <t>110101</t>
-        </is>
-      </c>
-      <c r="C36" t="inlineStr">
-        <is>
-          <t>ICA</t>
-        </is>
-      </c>
-      <c r="D36" t="inlineStr">
-        <is>
-          <t>ICA</t>
-        </is>
-      </c>
-      <c r="E36" t="inlineStr">
-        <is>
-          <t>ICA</t>
-        </is>
-      </c>
-      <c r="F36" t="inlineStr">
-        <is>
-          <t>-14.0800776</t>
-        </is>
-      </c>
-      <c r="G36" t="inlineStr">
-        <is>
-          <t>-75.7220342</t>
-        </is>
-      </c>
-      <c r="H36" t="inlineStr">
-        <is>
-          <t>Avenida Manuel Santana Chiri / Calle Jose Toribio Polo</t>
-        </is>
-      </c>
-      <c r="I36" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J36" t="inlineStr">
-        <is>
-          <t>110101</t>
-        </is>
-      </c>
-    </row>
-    <row r="37">
-      <c r="A37" t="inlineStr">
-        <is>
-          <t>l-64888</t>
-        </is>
-      </c>
-      <c r="B37" t="inlineStr">
-        <is>
-          <t>110101</t>
-        </is>
-      </c>
-      <c r="C37" t="inlineStr">
-        <is>
-          <t>ICA</t>
-        </is>
-      </c>
-      <c r="D37" t="inlineStr">
-        <is>
-          <t>ICA</t>
-        </is>
-      </c>
-      <c r="E37" t="inlineStr">
-        <is>
-          <t>ICA</t>
-        </is>
-      </c>
-      <c r="F37" t="inlineStr">
-        <is>
-          <t>-14.0596295</t>
-        </is>
-      </c>
-      <c r="G37" t="inlineStr">
-        <is>
-          <t>-75.7374522</t>
-        </is>
-      </c>
-      <c r="H37" t="inlineStr">
-        <is>
-          <t>Avenida Arenales / Pasaje Sucre</t>
-        </is>
-      </c>
-      <c r="I37" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J37" t="inlineStr">
-        <is>
-          <t>110101</t>
-        </is>
-      </c>
-    </row>
-    <row r="38">
-      <c r="A38" t="inlineStr">
-        <is>
-          <t>l-64892</t>
-        </is>
-      </c>
-      <c r="B38" t="inlineStr">
-        <is>
-          <t>110101</t>
-        </is>
-      </c>
-      <c r="C38" t="inlineStr">
-        <is>
-          <t>ICA</t>
-        </is>
-      </c>
-      <c r="D38" t="inlineStr">
-        <is>
-          <t>ICA</t>
-        </is>
-      </c>
-      <c r="E38" t="inlineStr">
-        <is>
-          <t>ICA</t>
-        </is>
-      </c>
-      <c r="F38" t="inlineStr">
-        <is>
-          <t>-14.0595609</t>
-        </is>
-      </c>
-      <c r="G38" t="inlineStr">
-        <is>
-          <t>-75.7376093</t>
-        </is>
-      </c>
-      <c r="H38" t="inlineStr">
-        <is>
-          <t>Avenida Arenales</t>
-        </is>
-      </c>
-      <c r="I38" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J38" t="inlineStr">
-        <is>
-          <t>110101</t>
-        </is>
-      </c>
-    </row>
-    <row r="39">
-      <c r="A39" t="inlineStr">
-        <is>
-          <t>l-64909</t>
-        </is>
-      </c>
-      <c r="B39" t="inlineStr">
-        <is>
-          <t>110101</t>
-        </is>
-      </c>
-      <c r="C39" t="inlineStr">
-        <is>
-          <t>ICA</t>
-        </is>
-      </c>
-      <c r="D39" t="inlineStr">
-        <is>
-          <t>ICA</t>
-        </is>
-      </c>
-      <c r="E39" t="inlineStr">
-        <is>
-          <t>ICA</t>
-        </is>
-      </c>
-      <c r="F39" t="inlineStr">
-        <is>
-          <t>-14.0663187</t>
-        </is>
-      </c>
-      <c r="G39" t="inlineStr">
-        <is>
-          <t>-75.7355003</t>
-        </is>
-      </c>
-      <c r="H39" t="inlineStr">
-        <is>
-          <t>Avenida Túpac Amaru / Calle Luis Medina</t>
-        </is>
-      </c>
-      <c r="I39" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J39" t="inlineStr">
-        <is>
-          <t>110101</t>
-        </is>
-      </c>
-    </row>
-    <row r="40">
-      <c r="A40" t="inlineStr">
-        <is>
-          <t>l-64910</t>
-        </is>
-      </c>
-      <c r="B40" t="inlineStr">
-        <is>
-          <t>110101</t>
-        </is>
-      </c>
-      <c r="C40" t="inlineStr">
-        <is>
-          <t>ICA</t>
-        </is>
-      </c>
-      <c r="D40" t="inlineStr">
-        <is>
-          <t>ICA</t>
-        </is>
-      </c>
-      <c r="E40" t="inlineStr">
-        <is>
-          <t>ICA</t>
-        </is>
-      </c>
-      <c r="F40" t="inlineStr">
-        <is>
-          <t>-14.0662872</t>
-        </is>
-      </c>
-      <c r="G40" t="inlineStr">
-        <is>
-          <t>-75.735388</t>
-        </is>
-      </c>
-      <c r="H40" t="inlineStr">
-        <is>
-          <t>Avenida Túpac Amaru / Calle Luis Medina</t>
-        </is>
-      </c>
-      <c r="I40" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J40" t="inlineStr">
-        <is>
-          <t>110101</t>
-        </is>
-      </c>
-    </row>
-    <row r="41">
-      <c r="A41" t="inlineStr">
-        <is>
-          <t>l-716584</t>
-        </is>
-      </c>
-      <c r="B41" t="inlineStr">
-        <is>
-          <t>110101</t>
-        </is>
-      </c>
-      <c r="C41" t="inlineStr">
-        <is>
-          <t>ICA</t>
-        </is>
-      </c>
-      <c r="D41" t="inlineStr">
-        <is>
-          <t>ICA</t>
-        </is>
-      </c>
-      <c r="E41" t="inlineStr">
-        <is>
-          <t>ICA</t>
-        </is>
-      </c>
-      <c r="F41" t="inlineStr">
-        <is>
-          <t>-14.0909207</t>
-        </is>
-      </c>
-      <c r="G41" t="inlineStr">
-        <is>
-          <t>-75.7441705</t>
-        </is>
-      </c>
-      <c r="H41" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="I41" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J41" t="inlineStr">
-        <is>
-          <t>110101</t>
-        </is>
-      </c>
-    </row>
-    <row r="42">
-      <c r="A42" t="inlineStr">
-        <is>
-          <t>l-761110</t>
-        </is>
-      </c>
-      <c r="B42" t="inlineStr">
-        <is>
-          <t>110101</t>
-        </is>
-      </c>
-      <c r="C42" t="inlineStr">
-        <is>
-          <t>ICA</t>
-        </is>
-      </c>
-      <c r="D42" t="inlineStr">
-        <is>
-          <t>ICA</t>
-        </is>
-      </c>
-      <c r="E42" t="inlineStr">
-        <is>
-          <t>ICA</t>
-        </is>
-      </c>
-      <c r="F42" t="inlineStr">
-        <is>
-          <t>-14.0661602</t>
-        </is>
-      </c>
-      <c r="G42" t="inlineStr">
-        <is>
-          <t>-75.7377193</t>
-        </is>
-      </c>
-      <c r="H42" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="I42" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J42" t="inlineStr">
-        <is>
-          <t>110101</t>
-        </is>
-      </c>
-    </row>
-    <row r="43">
-      <c r="A43" t="inlineStr">
-        <is>
-          <t>l-761111</t>
-        </is>
-      </c>
-      <c r="B43" t="inlineStr">
-        <is>
-          <t>110101</t>
-        </is>
-      </c>
-      <c r="C43" t="inlineStr">
-        <is>
-          <t>ICA</t>
-        </is>
-      </c>
-      <c r="D43" t="inlineStr">
-        <is>
-          <t>ICA</t>
-        </is>
-      </c>
-      <c r="E43" t="inlineStr">
-        <is>
-          <t>ICA</t>
-        </is>
-      </c>
-      <c r="F43" t="inlineStr">
-        <is>
-          <t>-14.0660718</t>
-        </is>
-      </c>
-      <c r="G43" t="inlineStr">
-        <is>
-          <t>-75.7379944</t>
-        </is>
-      </c>
-      <c r="H43" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="I43" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J43" t="inlineStr">
-        <is>
-          <t>110101</t>
-        </is>
-      </c>
-    </row>
-    <row r="44">
-      <c r="A44" t="inlineStr">
-        <is>
-          <t>l-781694</t>
-        </is>
-      </c>
-      <c r="B44" t="inlineStr">
-        <is>
-          <t>110101</t>
-        </is>
-      </c>
-      <c r="C44" t="inlineStr">
-        <is>
-          <t>ICA</t>
-        </is>
-      </c>
-      <c r="D44" t="inlineStr">
-        <is>
-          <t>ICA</t>
-        </is>
-      </c>
-      <c r="E44" t="inlineStr">
-        <is>
-          <t>ICA</t>
-        </is>
-      </c>
-      <c r="F44" t="inlineStr">
-        <is>
-          <t>-14.0660111</t>
-        </is>
-      </c>
-      <c r="G44" t="inlineStr">
-        <is>
-          <t>-75.7377665</t>
-        </is>
-      </c>
-      <c r="H44" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="I44" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J44" t="inlineStr">
         <is>
           <t>110101</t>
         </is>

--- a/Intersecciones/excels/ICA-ICA-ICA.xlsx
+++ b/Intersecciones/excels/ICA-ICA-ICA.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J25"/>
+  <dimension ref="A1:J26"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1728,6 +1728,58 @@
         </is>
       </c>
     </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>I-62400</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>110110</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>ICA</t>
+        </is>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>ICA</t>
+        </is>
+      </c>
+      <c r="E26" t="inlineStr">
+        <is>
+          <t>SAN JUAN BAUTISTA</t>
+        </is>
+      </c>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t>-14.0300809</t>
+        </is>
+      </c>
+      <c r="G26" t="inlineStr">
+        <is>
+          <t>-75.7368251</t>
+        </is>
+      </c>
+      <c r="H26" t="inlineStr">
+        <is>
+          <t>Calle s / n / Calle s / n</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J26" t="inlineStr">
+        <is>
+          <t>110101</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/Intersecciones/excels/ICA-ICA-ICA.xlsx
+++ b/Intersecciones/excels/ICA-ICA-ICA.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J26"/>
+  <dimension ref="A1:J30"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -518,7 +518,7 @@
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>Calle Caracas / Calle 3 de Octubre</t>
+          <t>3 de Octubre / Caracas</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
@@ -575,7 +575,7 @@
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
@@ -726,7 +726,7 @@
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>José Matías Manzanilla / Calle s / n</t>
+          <t>Fray Ramon Rojas / José Matías Manzanilla</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
@@ -778,12 +778,12 @@
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>José Matías Manzanilla / Calle s / n</t>
+          <t>Calle Servulo Gutierrez / José Matías Manzanilla</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
@@ -1558,7 +1558,7 @@
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>Avenida Jorge Chávez / Calle s / n</t>
+          <t>Avenida Jorge Chávez / Avenida Principal</t>
         </is>
       </c>
       <c r="I22" t="inlineStr">
@@ -1775,6 +1775,214 @@
         </is>
       </c>
       <c r="J26" t="inlineStr">
+        <is>
+          <t>110101</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>I-62401</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>110110</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>ICA</t>
+        </is>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>ICA</t>
+        </is>
+      </c>
+      <c r="E27" t="inlineStr">
+        <is>
+          <t>SAN JUAN BAUTISTA</t>
+        </is>
+      </c>
+      <c r="F27" t="inlineStr">
+        <is>
+          <t>-14.030091</t>
+        </is>
+      </c>
+      <c r="G27" t="inlineStr">
+        <is>
+          <t>-75.7393021</t>
+        </is>
+      </c>
+      <c r="H27" t="inlineStr">
+        <is>
+          <t>Calle s / n / Calle s / n</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J27" t="inlineStr">
+        <is>
+          <t>110101</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>I-495086</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>110110</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>ICA</t>
+        </is>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>ICA</t>
+        </is>
+      </c>
+      <c r="E28" t="inlineStr">
+        <is>
+          <t>SAN JUAN BAUTISTA</t>
+        </is>
+      </c>
+      <c r="F28" t="inlineStr">
+        <is>
+          <t>-14.0255088</t>
+        </is>
+      </c>
+      <c r="G28" t="inlineStr">
+        <is>
+          <t>-75.7389098</t>
+        </is>
+      </c>
+      <c r="H28" t="inlineStr">
+        <is>
+          <t>Calle s / n / Calle s / n</t>
+        </is>
+      </c>
+      <c r="I28" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J28" t="inlineStr">
+        <is>
+          <t>110101</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>I-205365</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>110111</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>ICA</t>
+        </is>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>ICA</t>
+        </is>
+      </c>
+      <c r="E29" t="inlineStr">
+        <is>
+          <t>SANTIAGO</t>
+        </is>
+      </c>
+      <c r="F29" t="inlineStr">
+        <is>
+          <t>-14.1840841</t>
+        </is>
+      </c>
+      <c r="G29" t="inlineStr">
+        <is>
+          <t>-75.6818954</t>
+        </is>
+      </c>
+      <c r="H29" t="inlineStr">
+        <is>
+          <t>Calle s / n / Calle s / n</t>
+        </is>
+      </c>
+      <c r="I29" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J29" t="inlineStr">
+        <is>
+          <t>110101</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>I-62245</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>110112</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>ICA</t>
+        </is>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>ICA</t>
+        </is>
+      </c>
+      <c r="E30" t="inlineStr">
+        <is>
+          <t>SUBTANJALLA</t>
+        </is>
+      </c>
+      <c r="F30" t="inlineStr">
+        <is>
+          <t>-14.0193146</t>
+        </is>
+      </c>
+      <c r="G30" t="inlineStr">
+        <is>
+          <t>-75.7582554</t>
+        </is>
+      </c>
+      <c r="H30" t="inlineStr">
+        <is>
+          <t>Avenida San Martín / Calle San Isidro</t>
+        </is>
+      </c>
+      <c r="I30" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J30" t="inlineStr">
         <is>
           <t>110101</t>
         </is>

--- a/Intersecciones/excels/ICA-ICA-ICA.xlsx
+++ b/Intersecciones/excels/ICA-ICA-ICA.xlsx
@@ -425,35 +425,35 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J30"/>
+  <dimension ref="A1:I30"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
+          <t>ubigeo_gestor</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>DEPARTAMENTO</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>PROVINCIA</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>DISTRITO</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
           <t>ID_INT</t>
         </is>
       </c>
-      <c r="B1" s="1" t="inlineStr">
-        <is>
-          <t>UBIGEO</t>
-        </is>
-      </c>
-      <c r="C1" s="1" t="inlineStr">
-        <is>
-          <t>DEPARTAMENTO</t>
-        </is>
-      </c>
-      <c r="D1" s="1" t="inlineStr">
-        <is>
-          <t>PROVINCIA</t>
-        </is>
-      </c>
-      <c r="E1" s="1" t="inlineStr">
-        <is>
-          <t>DISTRITO</t>
-        </is>
-      </c>
       <c r="F1" s="1" t="inlineStr">
         <is>
           <t>LATITUD</t>
@@ -472,40 +472,35 @@
       <c r="I1" s="1" t="inlineStr">
         <is>
           <t>Siniestro_fatal</t>
-        </is>
-      </c>
-      <c r="J1" s="1" t="inlineStr">
-        <is>
-          <t>ubigeo_gestor</t>
         </is>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
+          <t>110101</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>ICA</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>ICA</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>ICA</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
           <t>I-62755</t>
         </is>
       </c>
-      <c r="B2" t="inlineStr">
-        <is>
-          <t>110102</t>
-        </is>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>ICA</t>
-        </is>
-      </c>
-      <c r="D2" t="inlineStr">
-        <is>
-          <t>ICA</t>
-        </is>
-      </c>
-      <c r="E2" t="inlineStr">
-        <is>
-          <t>LA TINGUIÑA</t>
-        </is>
-      </c>
       <c r="F2" t="inlineStr">
         <is>
           <t>-14.040161</t>
@@ -524,40 +519,35 @@
       <c r="I2" t="inlineStr">
         <is>
           <t>0</t>
-        </is>
-      </c>
-      <c r="J2" t="inlineStr">
-        <is>
-          <t>110101</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
+          <t>110101</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>ICA</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>ICA</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>ICA</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
           <t>I-279460</t>
         </is>
       </c>
-      <c r="B3" t="inlineStr">
-        <is>
-          <t>110106</t>
-        </is>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>ICA</t>
-        </is>
-      </c>
-      <c r="D3" t="inlineStr">
-        <is>
-          <t>ICA</t>
-        </is>
-      </c>
-      <c r="E3" t="inlineStr">
-        <is>
-          <t>PARCONA</t>
-        </is>
-      </c>
       <c r="F3" t="inlineStr">
         <is>
           <t>-14.0681151</t>
@@ -576,40 +566,35 @@
       <c r="I3" t="inlineStr">
         <is>
           <t>1</t>
-        </is>
-      </c>
-      <c r="J3" t="inlineStr">
-        <is>
-          <t>110101</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
+          <t>110101</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>ICA</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>ICA</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>ICA</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
           <t>I-63663</t>
         </is>
       </c>
-      <c r="B4" t="inlineStr">
-        <is>
-          <t>110102</t>
-        </is>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>ICA</t>
-        </is>
-      </c>
-      <c r="D4" t="inlineStr">
-        <is>
-          <t>ICA</t>
-        </is>
-      </c>
-      <c r="E4" t="inlineStr">
-        <is>
-          <t>LA TINGUIÑA</t>
-        </is>
-      </c>
       <c r="F4" t="inlineStr">
         <is>
           <t>-14.0377339</t>
@@ -628,40 +613,35 @@
       <c r="I4" t="inlineStr">
         <is>
           <t>1</t>
-        </is>
-      </c>
-      <c r="J4" t="inlineStr">
-        <is>
-          <t>110101</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
+          <t>110101</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>ICA</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>ICA</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>ICA</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
           <t>I-365342</t>
         </is>
       </c>
-      <c r="B5" t="inlineStr">
-        <is>
-          <t>110112</t>
-        </is>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>ICA</t>
-        </is>
-      </c>
-      <c r="D5" t="inlineStr">
-        <is>
-          <t>ICA</t>
-        </is>
-      </c>
-      <c r="E5" t="inlineStr">
-        <is>
-          <t>SUBTANJALLA</t>
-        </is>
-      </c>
       <c r="F5" t="inlineStr">
         <is>
           <t>-14.0293972</t>
@@ -680,40 +660,35 @@
       <c r="I5" t="inlineStr">
         <is>
           <t>1</t>
-        </is>
-      </c>
-      <c r="J5" t="inlineStr">
-        <is>
-          <t>110101</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
+          <t>110101</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>ICA</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>ICA</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>ICA</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
           <t>I-555561</t>
         </is>
       </c>
-      <c r="B6" t="inlineStr">
-        <is>
-          <t>110101</t>
-        </is>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>ICA</t>
-        </is>
-      </c>
-      <c r="D6" t="inlineStr">
-        <is>
-          <t>ICA</t>
-        </is>
-      </c>
-      <c r="E6" t="inlineStr">
-        <is>
-          <t>ICA</t>
-        </is>
-      </c>
       <c r="F6" t="inlineStr">
         <is>
           <t>-14.0647557</t>
@@ -732,40 +707,35 @@
       <c r="I6" t="inlineStr">
         <is>
           <t>1</t>
-        </is>
-      </c>
-      <c r="J6" t="inlineStr">
-        <is>
-          <t>110101</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
+          <t>110101</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>ICA</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>ICA</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>ICA</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
           <t>I-620729</t>
         </is>
       </c>
-      <c r="B7" t="inlineStr">
-        <is>
-          <t>110101</t>
-        </is>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>ICA</t>
-        </is>
-      </c>
-      <c r="D7" t="inlineStr">
-        <is>
-          <t>ICA</t>
-        </is>
-      </c>
-      <c r="E7" t="inlineStr">
-        <is>
-          <t>ICA</t>
-        </is>
-      </c>
       <c r="F7" t="inlineStr">
         <is>
           <t>-14.0659359</t>
@@ -784,40 +754,35 @@
       <c r="I7" t="inlineStr">
         <is>
           <t>1</t>
-        </is>
-      </c>
-      <c r="J7" t="inlineStr">
-        <is>
-          <t>110101</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
+          <t>110101</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>ICA</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>ICA</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>ICA</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
           <t>I-62646</t>
         </is>
       </c>
-      <c r="B8" t="inlineStr">
-        <is>
-          <t>110101</t>
-        </is>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>ICA</t>
-        </is>
-      </c>
-      <c r="D8" t="inlineStr">
-        <is>
-          <t>ICA</t>
-        </is>
-      </c>
-      <c r="E8" t="inlineStr">
-        <is>
-          <t>ICA</t>
-        </is>
-      </c>
       <c r="F8" t="inlineStr">
         <is>
           <t>-14.0598238</t>
@@ -836,40 +801,35 @@
       <c r="I8" t="inlineStr">
         <is>
           <t>1</t>
-        </is>
-      </c>
-      <c r="J8" t="inlineStr">
-        <is>
-          <t>110101</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
+          <t>110101</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>ICA</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>ICA</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>ICA</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
           <t>I-64909</t>
         </is>
       </c>
-      <c r="B9" t="inlineStr">
-        <is>
-          <t>110101</t>
-        </is>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>ICA</t>
-        </is>
-      </c>
-      <c r="D9" t="inlineStr">
-        <is>
-          <t>ICA</t>
-        </is>
-      </c>
-      <c r="E9" t="inlineStr">
-        <is>
-          <t>ICA</t>
-        </is>
-      </c>
       <c r="F9" t="inlineStr">
         <is>
           <t>-14.0663187</t>
@@ -888,40 +848,35 @@
       <c r="I9" t="inlineStr">
         <is>
           <t>1</t>
-        </is>
-      </c>
-      <c r="J9" t="inlineStr">
-        <is>
-          <t>110101</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
+          <t>110101</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>ICA</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>ICA</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>ICA</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
           <t>I-281286</t>
         </is>
       </c>
-      <c r="B10" t="inlineStr">
-        <is>
-          <t>110110</t>
-        </is>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>ICA</t>
-        </is>
-      </c>
-      <c r="D10" t="inlineStr">
-        <is>
-          <t>ICA</t>
-        </is>
-      </c>
-      <c r="E10" t="inlineStr">
-        <is>
-          <t>SAN JUAN BAUTISTA</t>
-        </is>
-      </c>
       <c r="F10" t="inlineStr">
         <is>
           <t>-14.0047952</t>
@@ -940,40 +895,35 @@
       <c r="I10" t="inlineStr">
         <is>
           <t>1</t>
-        </is>
-      </c>
-      <c r="J10" t="inlineStr">
-        <is>
-          <t>110101</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
+          <t>110101</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>ICA</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>ICA</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>ICA</t>
+        </is>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
           <t>I-492495</t>
         </is>
       </c>
-      <c r="B11" t="inlineStr">
-        <is>
-          <t>110112</t>
-        </is>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>ICA</t>
-        </is>
-      </c>
-      <c r="D11" t="inlineStr">
-        <is>
-          <t>ICA</t>
-        </is>
-      </c>
-      <c r="E11" t="inlineStr">
-        <is>
-          <t>SUBTANJALLA</t>
-        </is>
-      </c>
       <c r="F11" t="inlineStr">
         <is>
           <t>-14.018372</t>
@@ -992,40 +942,35 @@
       <c r="I11" t="inlineStr">
         <is>
           <t>0</t>
-        </is>
-      </c>
-      <c r="J11" t="inlineStr">
-        <is>
-          <t>110101</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
+          <t>110101</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>ICA</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>ICA</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>ICA</t>
+        </is>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
           <t>I-62399</t>
         </is>
       </c>
-      <c r="B12" t="inlineStr">
-        <is>
-          <t>110110</t>
-        </is>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>ICA</t>
-        </is>
-      </c>
-      <c r="D12" t="inlineStr">
-        <is>
-          <t>ICA</t>
-        </is>
-      </c>
-      <c r="E12" t="inlineStr">
-        <is>
-          <t>SAN JUAN BAUTISTA</t>
-        </is>
-      </c>
       <c r="F12" t="inlineStr">
         <is>
           <t>-14.0300868</t>
@@ -1044,40 +989,35 @@
       <c r="I12" t="inlineStr">
         <is>
           <t>0</t>
-        </is>
-      </c>
-      <c r="J12" t="inlineStr">
-        <is>
-          <t>110101</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
+          <t>110101</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>ICA</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>ICA</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>ICA</t>
+        </is>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
           <t>I-490631</t>
         </is>
       </c>
-      <c r="B13" t="inlineStr">
-        <is>
-          <t>110110</t>
-        </is>
-      </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t>ICA</t>
-        </is>
-      </c>
-      <c r="D13" t="inlineStr">
-        <is>
-          <t>ICA</t>
-        </is>
-      </c>
-      <c r="E13" t="inlineStr">
-        <is>
-          <t>SAN JUAN BAUTISTA</t>
-        </is>
-      </c>
       <c r="F13" t="inlineStr">
         <is>
           <t>-14.0269422</t>
@@ -1096,40 +1036,35 @@
       <c r="I13" t="inlineStr">
         <is>
           <t>0</t>
-        </is>
-      </c>
-      <c r="J13" t="inlineStr">
-        <is>
-          <t>110101</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
+          <t>110101</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>ICA</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>ICA</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>ICA</t>
+        </is>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
           <t>I-490629</t>
         </is>
       </c>
-      <c r="B14" t="inlineStr">
-        <is>
-          <t>110110</t>
-        </is>
-      </c>
-      <c r="C14" t="inlineStr">
-        <is>
-          <t>ICA</t>
-        </is>
-      </c>
-      <c r="D14" t="inlineStr">
-        <is>
-          <t>ICA</t>
-        </is>
-      </c>
-      <c r="E14" t="inlineStr">
-        <is>
-          <t>SAN JUAN BAUTISTA</t>
-        </is>
-      </c>
       <c r="F14" t="inlineStr">
         <is>
           <t>-14.0258685</t>
@@ -1148,40 +1083,35 @@
       <c r="I14" t="inlineStr">
         <is>
           <t>0</t>
-        </is>
-      </c>
-      <c r="J14" t="inlineStr">
-        <is>
-          <t>110101</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
+          <t>110101</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>ICA</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>ICA</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>ICA</t>
+        </is>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
           <t>I-394660</t>
         </is>
       </c>
-      <c r="B15" t="inlineStr">
-        <is>
-          <t>110101</t>
-        </is>
-      </c>
-      <c r="C15" t="inlineStr">
-        <is>
-          <t>ICA</t>
-        </is>
-      </c>
-      <c r="D15" t="inlineStr">
-        <is>
-          <t>ICA</t>
-        </is>
-      </c>
-      <c r="E15" t="inlineStr">
-        <is>
-          <t>ICA</t>
-        </is>
-      </c>
       <c r="F15" t="inlineStr">
         <is>
           <t>-14.0910004</t>
@@ -1200,40 +1130,35 @@
       <c r="I15" t="inlineStr">
         <is>
           <t>1</t>
-        </is>
-      </c>
-      <c r="J15" t="inlineStr">
-        <is>
-          <t>110101</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
+          <t>110101</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>ICA</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>ICA</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>ICA</t>
+        </is>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
           <t>I-488935</t>
         </is>
       </c>
-      <c r="B16" t="inlineStr">
-        <is>
-          <t>110101</t>
-        </is>
-      </c>
-      <c r="C16" t="inlineStr">
-        <is>
-          <t>ICA</t>
-        </is>
-      </c>
-      <c r="D16" t="inlineStr">
-        <is>
-          <t>ICA</t>
-        </is>
-      </c>
-      <c r="E16" t="inlineStr">
-        <is>
-          <t>ICA</t>
-        </is>
-      </c>
       <c r="F16" t="inlineStr">
         <is>
           <t>-14.0740559</t>
@@ -1252,40 +1177,35 @@
       <c r="I16" t="inlineStr">
         <is>
           <t>1</t>
-        </is>
-      </c>
-      <c r="J16" t="inlineStr">
-        <is>
-          <t>110101</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
+          <t>110101</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>ICA</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>ICA</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>ICA</t>
+        </is>
+      </c>
+      <c r="E17" t="inlineStr">
+        <is>
           <t>I-62502</t>
         </is>
       </c>
-      <c r="B17" t="inlineStr">
-        <is>
-          <t>110101</t>
-        </is>
-      </c>
-      <c r="C17" t="inlineStr">
-        <is>
-          <t>ICA</t>
-        </is>
-      </c>
-      <c r="D17" t="inlineStr">
-        <is>
-          <t>ICA</t>
-        </is>
-      </c>
-      <c r="E17" t="inlineStr">
-        <is>
-          <t>ICA</t>
-        </is>
-      </c>
       <c r="F17" t="inlineStr">
         <is>
           <t>-14.0806734</t>
@@ -1304,40 +1224,35 @@
       <c r="I17" t="inlineStr">
         <is>
           <t>1</t>
-        </is>
-      </c>
-      <c r="J17" t="inlineStr">
-        <is>
-          <t>110101</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
+          <t>110101</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>ICA</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>ICA</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>ICA</t>
+        </is>
+      </c>
+      <c r="E18" t="inlineStr">
+        <is>
           <t>I-205359</t>
         </is>
       </c>
-      <c r="B18" t="inlineStr">
-        <is>
-          <t>110111</t>
-        </is>
-      </c>
-      <c r="C18" t="inlineStr">
-        <is>
-          <t>ICA</t>
-        </is>
-      </c>
-      <c r="D18" t="inlineStr">
-        <is>
-          <t>ICA</t>
-        </is>
-      </c>
-      <c r="E18" t="inlineStr">
-        <is>
-          <t>SANTIAGO</t>
-        </is>
-      </c>
       <c r="F18" t="inlineStr">
         <is>
           <t>-14.1746258</t>
@@ -1356,40 +1271,35 @@
       <c r="I18" t="inlineStr">
         <is>
           <t>0</t>
-        </is>
-      </c>
-      <c r="J18" t="inlineStr">
-        <is>
-          <t>110101</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
+          <t>110101</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>ICA</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>ICA</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>ICA</t>
+        </is>
+      </c>
+      <c r="E19" t="inlineStr">
+        <is>
           <t>I-64495</t>
         </is>
       </c>
-      <c r="B19" t="inlineStr">
-        <is>
-          <t>110101</t>
-        </is>
-      </c>
-      <c r="C19" t="inlineStr">
-        <is>
-          <t>ICA</t>
-        </is>
-      </c>
-      <c r="D19" t="inlineStr">
-        <is>
-          <t>ICA</t>
-        </is>
-      </c>
-      <c r="E19" t="inlineStr">
-        <is>
-          <t>ICA</t>
-        </is>
-      </c>
       <c r="F19" t="inlineStr">
         <is>
           <t>-14.0689648</t>
@@ -1408,40 +1318,35 @@
       <c r="I19" t="inlineStr">
         <is>
           <t>1</t>
-        </is>
-      </c>
-      <c r="J19" t="inlineStr">
-        <is>
-          <t>110101</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
+          <t>110101</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>ICA</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>ICA</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>ICA</t>
+        </is>
+      </c>
+      <c r="E20" t="inlineStr">
+        <is>
           <t>I-62243</t>
         </is>
       </c>
-      <c r="B20" t="inlineStr">
-        <is>
-          <t>110112</t>
-        </is>
-      </c>
-      <c r="C20" t="inlineStr">
-        <is>
-          <t>ICA</t>
-        </is>
-      </c>
-      <c r="D20" t="inlineStr">
-        <is>
-          <t>ICA</t>
-        </is>
-      </c>
-      <c r="E20" t="inlineStr">
-        <is>
-          <t>SUBTANJALLA</t>
-        </is>
-      </c>
       <c r="F20" t="inlineStr">
         <is>
           <t>-14.0199894</t>
@@ -1460,40 +1365,35 @@
       <c r="I20" t="inlineStr">
         <is>
           <t>0</t>
-        </is>
-      </c>
-      <c r="J20" t="inlineStr">
-        <is>
-          <t>110101</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
+          <t>110101</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>ICA</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>ICA</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>ICA</t>
+        </is>
+      </c>
+      <c r="E21" t="inlineStr">
+        <is>
           <t>I-399404</t>
         </is>
       </c>
-      <c r="B21" t="inlineStr">
-        <is>
-          <t>110110</t>
-        </is>
-      </c>
-      <c r="C21" t="inlineStr">
-        <is>
-          <t>ICA</t>
-        </is>
-      </c>
-      <c r="D21" t="inlineStr">
-        <is>
-          <t>ICA</t>
-        </is>
-      </c>
-      <c r="E21" t="inlineStr">
-        <is>
-          <t>SAN JUAN BAUTISTA</t>
-        </is>
-      </c>
       <c r="F21" t="inlineStr">
         <is>
           <t>-14.0319673</t>
@@ -1512,40 +1412,35 @@
       <c r="I21" t="inlineStr">
         <is>
           <t>0</t>
-        </is>
-      </c>
-      <c r="J21" t="inlineStr">
-        <is>
-          <t>110101</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
+          <t>110101</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>ICA</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>ICA</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>ICA</t>
+        </is>
+      </c>
+      <c r="E22" t="inlineStr">
+        <is>
           <t>I-490628</t>
         </is>
       </c>
-      <c r="B22" t="inlineStr">
-        <is>
-          <t>110110</t>
-        </is>
-      </c>
-      <c r="C22" t="inlineStr">
-        <is>
-          <t>ICA</t>
-        </is>
-      </c>
-      <c r="D22" t="inlineStr">
-        <is>
-          <t>ICA</t>
-        </is>
-      </c>
-      <c r="E22" t="inlineStr">
-        <is>
-          <t>SAN JUAN BAUTISTA</t>
-        </is>
-      </c>
       <c r="F22" t="inlineStr">
         <is>
           <t>-14.0282295</t>
@@ -1564,40 +1459,35 @@
       <c r="I22" t="inlineStr">
         <is>
           <t>0</t>
-        </is>
-      </c>
-      <c r="J22" t="inlineStr">
-        <is>
-          <t>110101</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
+          <t>110101</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>ICA</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>ICA</t>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>ICA</t>
+        </is>
+      </c>
+      <c r="E23" t="inlineStr">
+        <is>
           <t>I-399413</t>
         </is>
       </c>
-      <c r="B23" t="inlineStr">
-        <is>
-          <t>110110</t>
-        </is>
-      </c>
-      <c r="C23" t="inlineStr">
-        <is>
-          <t>ICA</t>
-        </is>
-      </c>
-      <c r="D23" t="inlineStr">
-        <is>
-          <t>ICA</t>
-        </is>
-      </c>
-      <c r="E23" t="inlineStr">
-        <is>
-          <t>SAN JUAN BAUTISTA</t>
-        </is>
-      </c>
       <c r="F23" t="inlineStr">
         <is>
           <t>-14.0332703</t>
@@ -1616,40 +1506,35 @@
       <c r="I23" t="inlineStr">
         <is>
           <t>0</t>
-        </is>
-      </c>
-      <c r="J23" t="inlineStr">
-        <is>
-          <t>110101</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
+          <t>110101</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>ICA</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>ICA</t>
+        </is>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>ICA</t>
+        </is>
+      </c>
+      <c r="E24" t="inlineStr">
+        <is>
           <t>I-399407</t>
         </is>
       </c>
-      <c r="B24" t="inlineStr">
-        <is>
-          <t>110110</t>
-        </is>
-      </c>
-      <c r="C24" t="inlineStr">
-        <is>
-          <t>ICA</t>
-        </is>
-      </c>
-      <c r="D24" t="inlineStr">
-        <is>
-          <t>ICA</t>
-        </is>
-      </c>
-      <c r="E24" t="inlineStr">
-        <is>
-          <t>SAN JUAN BAUTISTA</t>
-        </is>
-      </c>
       <c r="F24" t="inlineStr">
         <is>
           <t>-14.0361951</t>
@@ -1668,40 +1553,35 @@
       <c r="I24" t="inlineStr">
         <is>
           <t>0</t>
-        </is>
-      </c>
-      <c r="J24" t="inlineStr">
-        <is>
-          <t>110101</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
+          <t>110101</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>ICA</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>ICA</t>
+        </is>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>ICA</t>
+        </is>
+      </c>
+      <c r="E25" t="inlineStr">
+        <is>
           <t>I-399405</t>
         </is>
       </c>
-      <c r="B25" t="inlineStr">
-        <is>
-          <t>110110</t>
-        </is>
-      </c>
-      <c r="C25" t="inlineStr">
-        <is>
-          <t>ICA</t>
-        </is>
-      </c>
-      <c r="D25" t="inlineStr">
-        <is>
-          <t>ICA</t>
-        </is>
-      </c>
-      <c r="E25" t="inlineStr">
-        <is>
-          <t>SAN JUAN BAUTISTA</t>
-        </is>
-      </c>
       <c r="F25" t="inlineStr">
         <is>
           <t>-14.0292004</t>
@@ -1720,40 +1600,35 @@
       <c r="I25" t="inlineStr">
         <is>
           <t>0</t>
-        </is>
-      </c>
-      <c r="J25" t="inlineStr">
-        <is>
-          <t>110101</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
+          <t>110101</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>ICA</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>ICA</t>
+        </is>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>ICA</t>
+        </is>
+      </c>
+      <c r="E26" t="inlineStr">
+        <is>
           <t>I-62400</t>
         </is>
       </c>
-      <c r="B26" t="inlineStr">
-        <is>
-          <t>110110</t>
-        </is>
-      </c>
-      <c r="C26" t="inlineStr">
-        <is>
-          <t>ICA</t>
-        </is>
-      </c>
-      <c r="D26" t="inlineStr">
-        <is>
-          <t>ICA</t>
-        </is>
-      </c>
-      <c r="E26" t="inlineStr">
-        <is>
-          <t>SAN JUAN BAUTISTA</t>
-        </is>
-      </c>
       <c r="F26" t="inlineStr">
         <is>
           <t>-14.0300809</t>
@@ -1772,40 +1647,35 @@
       <c r="I26" t="inlineStr">
         <is>
           <t>0</t>
-        </is>
-      </c>
-      <c r="J26" t="inlineStr">
-        <is>
-          <t>110101</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
+          <t>110101</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>ICA</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>ICA</t>
+        </is>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>ICA</t>
+        </is>
+      </c>
+      <c r="E27" t="inlineStr">
+        <is>
           <t>I-62401</t>
         </is>
       </c>
-      <c r="B27" t="inlineStr">
-        <is>
-          <t>110110</t>
-        </is>
-      </c>
-      <c r="C27" t="inlineStr">
-        <is>
-          <t>ICA</t>
-        </is>
-      </c>
-      <c r="D27" t="inlineStr">
-        <is>
-          <t>ICA</t>
-        </is>
-      </c>
-      <c r="E27" t="inlineStr">
-        <is>
-          <t>SAN JUAN BAUTISTA</t>
-        </is>
-      </c>
       <c r="F27" t="inlineStr">
         <is>
           <t>-14.030091</t>
@@ -1824,40 +1694,35 @@
       <c r="I27" t="inlineStr">
         <is>
           <t>0</t>
-        </is>
-      </c>
-      <c r="J27" t="inlineStr">
-        <is>
-          <t>110101</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
+          <t>110101</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>ICA</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>ICA</t>
+        </is>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>ICA</t>
+        </is>
+      </c>
+      <c r="E28" t="inlineStr">
+        <is>
           <t>I-495086</t>
         </is>
       </c>
-      <c r="B28" t="inlineStr">
-        <is>
-          <t>110110</t>
-        </is>
-      </c>
-      <c r="C28" t="inlineStr">
-        <is>
-          <t>ICA</t>
-        </is>
-      </c>
-      <c r="D28" t="inlineStr">
-        <is>
-          <t>ICA</t>
-        </is>
-      </c>
-      <c r="E28" t="inlineStr">
-        <is>
-          <t>SAN JUAN BAUTISTA</t>
-        </is>
-      </c>
       <c r="F28" t="inlineStr">
         <is>
           <t>-14.0255088</t>
@@ -1876,40 +1741,35 @@
       <c r="I28" t="inlineStr">
         <is>
           <t>0</t>
-        </is>
-      </c>
-      <c r="J28" t="inlineStr">
-        <is>
-          <t>110101</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
+          <t>110101</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>ICA</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>ICA</t>
+        </is>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>ICA</t>
+        </is>
+      </c>
+      <c r="E29" t="inlineStr">
+        <is>
           <t>I-205365</t>
         </is>
       </c>
-      <c r="B29" t="inlineStr">
-        <is>
-          <t>110111</t>
-        </is>
-      </c>
-      <c r="C29" t="inlineStr">
-        <is>
-          <t>ICA</t>
-        </is>
-      </c>
-      <c r="D29" t="inlineStr">
-        <is>
-          <t>ICA</t>
-        </is>
-      </c>
-      <c r="E29" t="inlineStr">
-        <is>
-          <t>SANTIAGO</t>
-        </is>
-      </c>
       <c r="F29" t="inlineStr">
         <is>
           <t>-14.1840841</t>
@@ -1928,40 +1788,35 @@
       <c r="I29" t="inlineStr">
         <is>
           <t>0</t>
-        </is>
-      </c>
-      <c r="J29" t="inlineStr">
-        <is>
-          <t>110101</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
+          <t>110101</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>ICA</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>ICA</t>
+        </is>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>ICA</t>
+        </is>
+      </c>
+      <c r="E30" t="inlineStr">
+        <is>
           <t>I-62245</t>
         </is>
       </c>
-      <c r="B30" t="inlineStr">
-        <is>
-          <t>110112</t>
-        </is>
-      </c>
-      <c r="C30" t="inlineStr">
-        <is>
-          <t>ICA</t>
-        </is>
-      </c>
-      <c r="D30" t="inlineStr">
-        <is>
-          <t>ICA</t>
-        </is>
-      </c>
-      <c r="E30" t="inlineStr">
-        <is>
-          <t>SUBTANJALLA</t>
-        </is>
-      </c>
       <c r="F30" t="inlineStr">
         <is>
           <t>-14.0193146</t>
@@ -1980,11 +1835,6 @@
       <c r="I30" t="inlineStr">
         <is>
           <t>0</t>
-        </is>
-      </c>
-      <c r="J30" t="inlineStr">
-        <is>
-          <t>110101</t>
         </is>
       </c>
     </row>

--- a/Intersecciones/excels/ICA-ICA-ICA.xlsx
+++ b/Intersecciones/excels/ICA-ICA-ICA.xlsx
@@ -451,7 +451,7 @@
       </c>
       <c r="E1" s="1" t="inlineStr">
         <is>
-          <t>ID_INT</t>
+          <t>Codigo</t>
         </is>
       </c>
       <c r="F1" s="1" t="inlineStr">

--- a/Intersecciones/excels/ICA-ICA-ICA.xlsx
+++ b/Intersecciones/excels/ICA-ICA-ICA.xlsx
@@ -1,13 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -17,16 +17,13 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="2">
+  <fonts count="1">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
       <color theme="1"/>
       <sz val="11"/>
       <scheme val="minor"/>
-    </font>
-    <font>
-      <b val="1"/>
     </font>
   </fonts>
   <fills count="2">
@@ -37,7 +34,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="2">
+  <borders count="1">
     <border>
       <left/>
       <right/>
@@ -45,21 +42,12 @@
       <bottom/>
       <diagonal/>
     </border>
-    <border>
-      <left style="thin"/>
-      <right style="thin"/>
-      <top style="thin"/>
-      <bottom style="thin"/>
-    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -429,47 +417,47 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="inlineStr">
+      <c r="A1" t="inlineStr">
         <is>
           <t>ubigeo_gestor</t>
         </is>
       </c>
-      <c r="B1" s="1" t="inlineStr">
+      <c r="B1" t="inlineStr">
         <is>
           <t>DEPARTAMENTO</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
+      <c r="C1" t="inlineStr">
         <is>
           <t>PROVINCIA</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="D1" t="inlineStr">
         <is>
           <t>DISTRITO</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="E1" t="inlineStr">
         <is>
           <t>Codigo</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="F1" t="inlineStr">
         <is>
           <t>LATITUD</t>
         </is>
       </c>
-      <c r="G1" s="1" t="inlineStr">
+      <c r="G1" t="inlineStr">
         <is>
           <t>LONGITUD</t>
         </is>
       </c>
-      <c r="H1" s="1" t="inlineStr">
+      <c r="H1" t="inlineStr">
         <is>
           <t>Vias</t>
         </is>
       </c>
-      <c r="I1" s="1" t="inlineStr">
+      <c r="I1" t="inlineStr">
         <is>
           <t>Siniestro_fatal</t>
         </is>

--- a/Intersecciones/excels/ICA-ICA-ICA.xlsx
+++ b/Intersecciones/excels/ICA-ICA-ICA.xlsx
@@ -679,17 +679,17 @@
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>-14.0647557</t>
+          <t>-14.030091</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>-75.7336359</t>
+          <t>-75.7393021</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>Fray Ramon Rojas / José Matías Manzanilla</t>
+          <t>Calle s / n / Calle s / n</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
@@ -820,17 +820,17 @@
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>-14.0663187</t>
+          <t>-14.0681151</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>-75.7355003</t>
+          <t>-75.6829878</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>Avenida Túpac Amaru / Calle Luis Medina</t>
+          <t>Avenida José Matías Manzanilla / Avenida Sinchi Roca</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">

--- a/Intersecciones/excels/ICA-ICA-ICA.xlsx
+++ b/Intersecciones/excels/ICA-ICA-ICA.xlsx
@@ -486,27 +486,27 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>I-62755</t>
+          <t>I-64909</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>-14.040161</t>
+          <t>-14.0681151</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>-75.706799</t>
+          <t>-75.6829878</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>3 de Octubre / Caracas</t>
+          <t>Avenida José Matías Manzanilla / Avenida Sinchi Roca</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
     </row>
@@ -533,22 +533,22 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>I-279460</t>
+          <t>I-64495</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>-14.0681151</t>
+          <t>-14.0689648</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>-75.6829878</t>
+          <t>-75.7354703</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>Avenida José Matías Manzanilla / Avenida Sinchi Roca</t>
+          <t>Avenida Túpac Amaru / Calle s / n</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
@@ -627,27 +627,27 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>I-365342</t>
+          <t>I-62755</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>-14.0293972</t>
+          <t>-14.040161</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>-75.7543906</t>
+          <t>-75.706799</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>Primavera / Calle s / n</t>
+          <t>Calle Caracas / Calle 3 de Octubre</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
     </row>
@@ -674,22 +674,22 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>I-555561</t>
+          <t>I-62646</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>-14.030091</t>
+          <t>-14.0598238</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>-75.7393021</t>
+          <t>-75.7370205</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>Calle s / n / Calle s / n</t>
+          <t>Avenida Abraham Valdelomar / Avenida Arenales</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
@@ -721,22 +721,22 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>I-620729</t>
+          <t>I-62502</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>-14.0659359</t>
+          <t>-14.0806734</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>-75.7376298</t>
+          <t>-75.7322198</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>Calle Servulo Gutierrez / José Matías Manzanilla</t>
+          <t>Calle s / n / Calle s / n</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
@@ -768,27 +768,27 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>I-62646</t>
+          <t>I-62401</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>-14.0598238</t>
+          <t>-14.030091</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>-75.7370205</t>
+          <t>-75.7393021</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>Avenida Abraham Valdelomar / Avenida Arenales</t>
+          <t>Calle s / n / Calle s / n</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
     </row>
@@ -815,27 +815,27 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>I-64909</t>
+          <t>I-62400</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>-14.0681151</t>
+          <t>-14.0300809</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>-75.6829878</t>
+          <t>-75.7368251</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>Avenida José Matías Manzanilla / Avenida Sinchi Roca</t>
+          <t>Calle s / n / Calle s / n</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
     </row>
@@ -862,17 +862,17 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>I-281286</t>
+          <t>I-62399</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>-14.0047952</t>
+          <t>-14.0300868</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>-75.7530311</t>
+          <t>-75.7379605</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
@@ -882,7 +882,7 @@
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
     </row>
@@ -909,22 +909,22 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>I-492495</t>
+          <t>I-62245</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>-14.018372</t>
+          <t>-14.0193146</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>-75.7652824</t>
+          <t>-75.7582554</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>Calle s / n / Calle s / n</t>
+          <t>Avenida San Martín / Calle San Isidro</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
@@ -956,22 +956,22 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>I-62399</t>
+          <t>I-62243</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>-14.0300868</t>
+          <t>-14.0199894</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>-75.7379605</t>
+          <t>-75.7544522</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>Calle s / n / Calle s / n</t>
+          <t>Avenida San Martín / Calle General Salas</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
@@ -1003,27 +1003,27 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>I-490631</t>
+          <t>I-620729</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>-14.0269422</t>
+          <t>-14.0659359</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>-75.7352301</t>
+          <t>-75.7376298</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>Avenida Jorge Chávez / Calle s / n</t>
+          <t>José Matías Manzanilla / Calle s / n</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
     </row>
@@ -1050,27 +1050,27 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>I-490629</t>
+          <t>I-555561</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>-14.0258685</t>
+          <t>-14.030091</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>-75.7346654</t>
+          <t>-75.7393021</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>Avenida Jorge Chávez / Calle s / n</t>
+          <t>Calle s / n / Calle s / n</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
     </row>
@@ -1097,17 +1097,17 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>I-394660</t>
+          <t>I-495086</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>-14.0910004</t>
+          <t>-14.0255088</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>-75.743717</t>
+          <t>-75.7389098</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
@@ -1117,7 +1117,7 @@
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
     </row>
@@ -1144,17 +1144,17 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>I-488935</t>
+          <t>I-492495</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>-14.0740559</t>
+          <t>-14.018372</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>-75.7848412</t>
+          <t>-75.7652824</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
@@ -1164,7 +1164,7 @@
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
     </row>
@@ -1191,27 +1191,27 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>I-62502</t>
+          <t>I-490631</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>-14.0806734</t>
+          <t>-14.0269422</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>-75.7322198</t>
+          <t>-75.7352301</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>Calle s / n / Calle s / n</t>
+          <t>Avenida Jorge Chávez / Calle s / n</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
     </row>
@@ -1238,22 +1238,22 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>I-205359</t>
+          <t>I-490629</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>-14.1746258</t>
+          <t>-14.0258685</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>-75.6858999</t>
+          <t>-75.7346654</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>Calle s / n / Calle s / n</t>
+          <t>Avenida Jorge Chávez / Calle s / n</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
@@ -1285,27 +1285,27 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>I-64495</t>
+          <t>I-490628</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>-14.0689648</t>
+          <t>-14.0282295</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>-75.7354703</t>
+          <t>-75.7357678</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>Avenida Túpac Amaru / Calle s / n</t>
+          <t>Avenida Jorge Chávez / Calle s / n</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
     </row>
@@ -1332,27 +1332,27 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>I-62243</t>
+          <t>I-488935</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>-14.0199894</t>
+          <t>-14.0740559</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>-75.7544522</t>
+          <t>-75.7848412</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>Avenida San Martín / Calle General Salas</t>
+          <t>Calle s / n / Calle s / n</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
     </row>
@@ -1379,17 +1379,17 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>I-399404</t>
+          <t>I-399413</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>-14.0319673</t>
+          <t>-14.0332703</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>-75.7349809</t>
+          <t>-75.7347087</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
@@ -1426,22 +1426,22 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>I-490628</t>
+          <t>I-399407</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>-14.0282295</t>
+          <t>-14.0361951</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>-75.7357678</t>
+          <t>-75.7340117</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>Avenida Jorge Chávez / Avenida Principal</t>
+          <t>Andrés Avelino Cáceres / Avenida Jorge Chávez</t>
         </is>
       </c>
       <c r="I22" t="inlineStr">
@@ -1473,22 +1473,22 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>I-399413</t>
+          <t>I-399405</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>-14.0332703</t>
+          <t>-14.0292004</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>-75.7347087</t>
+          <t>-75.735677</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>Avenida Jorge Chávez / Calle s / n</t>
+          <t>Avenida Jorge Chávez / Calle 7</t>
         </is>
       </c>
       <c r="I23" t="inlineStr">
@@ -1520,22 +1520,22 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>I-399407</t>
+          <t>I-399404</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>-14.0361951</t>
+          <t>-14.0319673</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>-75.7340117</t>
+          <t>-75.7349809</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>Andrés Avelino Cáceres / Avenida Jorge Chávez</t>
+          <t>Avenida Jorge Chávez / Calle s / n</t>
         </is>
       </c>
       <c r="I24" t="inlineStr">
@@ -1567,27 +1567,27 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>I-399405</t>
+          <t>I-394660</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>-14.0292004</t>
+          <t>-14.0910004</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>-75.735677</t>
+          <t>-75.743717</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>Avenida Jorge Chávez / Calle 7</t>
+          <t>Calle s / n / Calle s / n</t>
         </is>
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
     </row>
@@ -1614,27 +1614,27 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>I-62400</t>
+          <t>I-365342</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>-14.0300809</t>
+          <t>-14.0293972</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>-75.7368251</t>
+          <t>-75.7543906</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>Calle s / n / Calle s / n</t>
+          <t>Primavera / Calle s / n</t>
         </is>
       </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
     </row>
@@ -1661,17 +1661,17 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>I-62401</t>
+          <t>I-281286</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>-14.030091</t>
+          <t>-14.0047952</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>-75.7393021</t>
+          <t>-75.7530311</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
@@ -1681,7 +1681,7 @@
       </c>
       <c r="I27" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
     </row>
@@ -1708,27 +1708,27 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>I-495086</t>
+          <t>I-279460</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>-14.0255088</t>
+          <t>-14.0681151</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>-75.7389098</t>
+          <t>-75.6829878</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>Calle s / n / Calle s / n</t>
+          <t>Avenida José Matías Manzanilla / Avenida Sinchi Roca</t>
         </is>
       </c>
       <c r="I28" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
     </row>
@@ -1802,22 +1802,22 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>I-62245</t>
+          <t>I-205359</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>-14.0193146</t>
+          <t>-14.1746258</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>-75.7582554</t>
+          <t>-75.6858999</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>Avenida San Martín / Calle San Isidro</t>
+          <t>Calle s / n / Calle s / n</t>
         </is>
       </c>
       <c r="I30" t="inlineStr">
